--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>644.49</v>
+        <v>650.61</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10148.29</v>
+        <v>10244.68</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9666.190000000001</v>
+        <v>9758.01</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>30169.39</v>
+        <v>30455.97</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3109.66</v>
+        <v>3139.2</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>592.9299999999999</v>
+        <v>598.5599999999999</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>17895.31</v>
+        <v>18065.3</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>107.28</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>36570.39</v>
+        <v>36917.76</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>31579.96</v>
+        <v>31879.94</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9595.469999999999</v>
+        <v>9686.610000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>78949.91</v>
+        <v>79699.85000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>395.29</v>
+        <v>399.04</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>17185.41</v>
+        <v>17252.49</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>15113.86</v>
+        <v>15172.85</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9179.66</v>
+        <v>9215.5</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6333.26</v>
+        <v>6357.98</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>328.43</v>
+        <v>329.71</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>505.28</v>
+        <v>507.25</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1186.35</v>
+        <v>1190.99</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5203.73</v>
+        <v>5224.04</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1396.39</v>
+        <v>1401.84</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>612.26</v>
+        <v>614.65</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8373.950000000001</v>
+        <v>8406.639999999999</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3364.63</v>
+        <v>3377.76</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>435.8</v>
+        <v>437.5</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6424.84</v>
+        <v>6449.92</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>24479.11</v>
+        <v>24574.66</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5603.86</v>
+        <v>5625.74</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6765</v>
+        <v>6791.41</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5816.69</v>
+        <v>5875.19</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>842.13</v>
+        <v>850.6</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>8421.32</v>
+        <v>8506.02</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>107.41</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>20408.82</v>
+        <v>20614.08</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>151187.37</v>
+        <v>152707.94</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1158.98</v>
+        <v>1170.64</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>859.3200000000001</v>
+        <v>867.96</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2736.27</v>
+        <v>2763.79</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>859.3200000000001</v>
+        <v>867.96</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1444.26</v>
+        <v>1458.78</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7304.45</v>
+        <v>7377.59</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16175.26</v>
+        <v>16337.23</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5370.74</v>
+        <v>5424.52</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5239.75</v>
+        <v>5292.22</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>982.09</v>
+        <v>991.9299999999999</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>24382.36</v>
+        <v>24626.52</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>57937.66</v>
+        <v>58517.82</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>714.97</v>
+        <v>722.13</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>45697.47</v>
+        <v>46155.07</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>501.07</v>
+        <v>506.09</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>11219.31</v>
+        <v>11331.66</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3444.85</v>
+        <v>3479.34</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>510.22</v>
+        <v>512.8200000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1326.57</v>
+        <v>1333.33</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>31902.21</v>
+        <v>32064.78</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8207.639999999999</v>
+        <v>8249.459999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7848.38</v>
+        <v>7888.38</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>626.34</v>
+        <v>629.53</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1611.22</v>
+        <v>1619.43</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7489.71</v>
+        <v>7527.88</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>68410.63</v>
+        <v>68759.23</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>18790.08</v>
+        <v>18863.22</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>44039.31</v>
+        <v>44210.75</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>739819.76</v>
+        <v>742699.71</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>74198.74000000001</v>
+        <v>74487.58</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9902.68</v>
+        <v>9941.23</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>12526.72</v>
+        <v>12575.48</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>15579.98</v>
+        <v>15640.63</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3451.24</v>
+        <v>3464.68</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>6426.52</v>
+        <v>6393.97</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>29925.6</v>
+        <v>29774</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>16853.01</v>
+        <v>16767.64</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>75190.39</v>
+        <v>74809.5</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>18411.12</v>
+        <v>18317.85</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>21536.9</v>
+        <v>21427.81</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>12006.7</v>
+        <v>11945.88</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>106</v>
+        <v>105.47</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5262.17</v>
+        <v>5235.51</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>221.06</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>37578.56</v>
+        <v>37388.2</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>48411.56</v>
+        <v>48166.32</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1960.32</v>
+        <v>1950.39</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>12889.78</v>
+        <v>12824.49</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>20790.14</v>
+        <v>20684.83</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>15914.58</v>
+        <v>15833.97</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>22307.56</v>
+        <v>22194.56</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1074.15</v>
+        <v>1068.71</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>263.18</v>
+        <v>261.85</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>18790.08</v>
+        <v>18694.89</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>161.12</v>
+        <v>160.31</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>254268.89</v>
+        <v>252980.85</v>
       </c>
     </row>
     <row r="94">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5102.21</v>
+        <v>5113.08</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5661.33</v>
+        <v>5673.4</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2675.6</v>
+        <v>2681.3</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3061.32</v>
+        <v>3067.85</v>
       </c>
     </row>
     <row r="98">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8116.08</v>
+        <v>8133.38</v>
       </c>
     </row>
     <row r="99">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>25905.19</v>
+        <v>25960.4</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10017.17</v>
+        <v>10038.52</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5933.87</v>
+        <v>5946.52</v>
       </c>
     </row>
     <row r="102">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3951.71</v>
+        <v>3960.13</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>14732.05</v>
+        <v>14763.45</v>
       </c>
     </row>
     <row r="104">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>277.47</v>
+        <v>278.06</v>
       </c>
     </row>
     <row r="105">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>15406.43</v>
+        <v>15439.27</v>
       </c>
     </row>
     <row r="106">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2024.28</v>
+        <v>2028.59</v>
       </c>
     </row>
     <row r="107">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>45608.21</v>
+        <v>45705.41</v>
       </c>
     </row>
     <row r="108">
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>14227.61</v>
+        <v>14320.37</v>
       </c>
     </row>
     <row r="109">
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4323.45</v>
+        <v>4351.63</v>
       </c>
     </row>
     <row r="110">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>322.24</v>
+        <v>324.34</v>
       </c>
     </row>
     <row r="111">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>966.73</v>
+        <v>973.04</v>
       </c>
     </row>
     <row r="112">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>15069.96</v>
+        <v>15168.21</v>
       </c>
     </row>
     <row r="113">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2685.37</v>
+        <v>2702.88</v>
       </c>
     </row>
     <row r="114">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>12079.44</v>
+        <v>12158.19</v>
       </c>
     </row>
     <row r="115">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3077.36</v>
+        <v>3097.42</v>
       </c>
     </row>
     <row r="116">
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>11594.73</v>
+        <v>11670.32</v>
       </c>
     </row>
     <row r="117">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>15216.28</v>
+        <v>15315.48</v>
       </c>
     </row>
     <row r="118">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>5237.14</v>
+        <v>5249.15</v>
       </c>
     </row>
     <row r="119">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5370.74</v>
+        <v>5383.06</v>
       </c>
     </row>
     <row r="120">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>28560.92</v>
+        <v>28626.42</v>
       </c>
     </row>
     <row r="121">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>14156.85</v>
+        <v>14189.31</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>9081.870000000001</v>
+        <v>9102.700000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>31872.97</v>
+        <v>31946.06</v>
       </c>
     </row>
     <row r="124">
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2040.88</v>
+        <v>2045.56</v>
       </c>
     </row>
     <row r="125">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>22172.29</v>
+        <v>22223.14</v>
       </c>
     </row>
     <row r="126">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>568.4400000000001</v>
+        <v>569.74</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>735.8099999999999</v>
+        <v>737.5</v>
       </c>
     </row>
     <row r="128">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2056.19</v>
+        <v>2060.9</v>
       </c>
     </row>
     <row r="129">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3236.78</v>
+        <v>3244.21</v>
       </c>
     </row>
     <row r="130">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>42374.52</v>
+        <v>42471.7</v>
       </c>
     </row>
     <row r="131">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>306.13</v>
+        <v>308.18</v>
       </c>
     </row>
     <row r="132">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>18796.4</v>
+        <v>18922.21</v>
       </c>
     </row>
     <row r="133">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>27512.47</v>
+        <v>27696.62</v>
       </c>
     </row>
     <row r="134">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>41960.52</v>
+        <v>42241.38</v>
       </c>
     </row>
     <row r="135">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2217.27</v>
+        <v>2232.11</v>
       </c>
     </row>
     <row r="136">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1958.5</v>
+        <v>1971.61</v>
       </c>
     </row>
     <row r="137">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>40817.64</v>
+        <v>41090.85</v>
       </c>
     </row>
     <row r="138">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>386.69</v>
+        <v>389.28</v>
       </c>
     </row>
     <row r="139">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>30854.68</v>
+        <v>31061.2</v>
       </c>
     </row>
     <row r="140">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>863.09</v>
+        <v>868.87</v>
       </c>
     </row>
     <row r="141">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>470.78</v>
+        <v>473.93</v>
       </c>
     </row>
     <row r="142">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1073.54</v>
+        <v>1080.73</v>
       </c>
     </row>
     <row r="143">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>6315.99</v>
+        <v>6358.27</v>
       </c>
     </row>
     <row r="144">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>9271.879999999999</v>
+        <v>9333.940000000001</v>
       </c>
     </row>
     <row r="145">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>7077.39</v>
+        <v>7124.76</v>
       </c>
     </row>
     <row r="146">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>14501</v>
+        <v>14598.07</v>
       </c>
     </row>
     <row r="147">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>322.24</v>
+        <v>324.4</v>
       </c>
     </row>
     <row r="148">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>16460</v>
+        <v>16570.18</v>
       </c>
     </row>
     <row r="149">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>43879.31</v>
+        <v>44186.39</v>
       </c>
     </row>
     <row r="150">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>10271.91</v>
+        <v>10343.8</v>
       </c>
     </row>
     <row r="151">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3742.33</v>
+        <v>3768.52</v>
       </c>
     </row>
     <row r="152">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>13946.76</v>
+        <v>14044.37</v>
       </c>
     </row>
     <row r="153">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>285.94</v>
+        <v>287.95</v>
       </c>
     </row>
     <row r="154">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>12436.19</v>
+        <v>12523.22</v>
       </c>
     </row>
     <row r="155">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>55942.86</v>
+        <v>56334.37</v>
       </c>
     </row>
     <row r="156">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>27039.54</v>
+        <v>27228.77</v>
       </c>
     </row>
     <row r="157">
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>7247.6</v>
+        <v>7298.32</v>
       </c>
     </row>
     <row r="158">
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>25810.31</v>
+        <v>25990.94</v>
       </c>
     </row>
     <row r="159">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3219.37</v>
+        <v>3241.9</v>
       </c>
     </row>
     <row r="160">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3158</v>
+        <v>3180.1</v>
       </c>
     </row>
     <row r="161">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>9680.309999999999</v>
+        <v>9748.059999999999</v>
       </c>
     </row>
     <row r="162">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>161.12</v>
+        <v>162.25</v>
       </c>
     </row>
     <row r="163">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>14394.45</v>
+        <v>14348.99</v>
       </c>
     </row>
     <row r="164">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>10326.65</v>
+        <v>10294.03</v>
       </c>
     </row>
     <row r="165">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>45218.3</v>
+        <v>45075.47</v>
       </c>
     </row>
     <row r="166">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>24402.89</v>
+        <v>24325.81</v>
       </c>
     </row>
     <row r="167">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>513.14</v>
+        <v>511.52</v>
       </c>
     </row>
     <row r="168">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>18302.69</v>
+        <v>18244.88</v>
       </c>
     </row>
     <row r="169">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>193.35</v>
+        <v>192.74</v>
       </c>
     </row>
     <row r="170">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>10808.67</v>
+        <v>10774.53</v>
       </c>
     </row>
     <row r="171">
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>347.38</v>
+        <v>346.28</v>
       </c>
     </row>
     <row r="172">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5467.02</v>
+        <v>5449.75</v>
       </c>
     </row>
     <row r="173">
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>20331.16</v>
+        <v>20266.94</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2362.18</v>
+        <v>2357.04</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>31688.92</v>
+        <v>31619.97</v>
       </c>
     </row>
     <row r="176">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>22557.12</v>
+        <v>22508.04</v>
       </c>
     </row>
     <row r="177">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>273.08</v>
+        <v>272.49</v>
       </c>
     </row>
     <row r="178">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>232.66</v>
+        <v>232.15</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3286.89</v>
+        <v>3279.74</v>
       </c>
     </row>
     <row r="180">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2050.09</v>
+        <v>2045.63</v>
       </c>
     </row>
     <row r="181">
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>343.73</v>
+        <v>342.98</v>
       </c>
     </row>
     <row r="182">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>15228.28</v>
+        <v>15195.15</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>161.12</v>
+        <v>160.77</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>4004.79</v>
+        <v>3996.08</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>15433.37</v>
+        <v>15399.79</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>47009.43</v>
+        <v>46907.15</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2353.91</v>
+        <v>2348.79</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>6388.63</v>
+        <v>6374.73</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>6699.92</v>
+        <v>6685.34</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>8756.6</v>
+        <v>8737.549999999999</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>367.36</v>
+        <v>366.56</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>23377.07</v>
+        <v>23326.21</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>306.13</v>
+        <v>305.47</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>14902.59</v>
+        <v>14872.71</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>4099.67</v>
+        <v>4091.45</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>5112.95</v>
+        <v>5102.7</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>306.13</v>
+        <v>305.52</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>26854.78</v>
+        <v>26800.95</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>595.02</v>
+        <v>593.83</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>19002.09</v>
+        <v>18963.99</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2739.08</v>
+        <v>2733.59</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>214.83</v>
+        <v>214.4</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>16905.81</v>
+        <v>16871.92</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>12135.13</v>
+        <v>12110.8</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>859.3200000000001</v>
+        <v>857.6</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>15298.58</v>
+        <v>15267.91</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>41988.72</v>
+        <v>41904.55</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>66.33</v>
+        <v>65.94</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>204.09</v>
+        <v>202.91</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2156.89</v>
+        <v>2144.41</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>33316.62</v>
+        <v>33123.78</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>12889.78</v>
+        <v>12815.17</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>20855.41</v>
+        <v>20734.69</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>163.27</v>
+        <v>162.33</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>16600.96</v>
+        <v>16504.88</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3831.7</v>
+        <v>3809.52</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>804.48</v>
+        <v>799.83</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>268.54</v>
+        <v>266.98</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>586.49</v>
+        <v>583.09</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3965.86</v>
+        <v>3942.91</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>5112.95</v>
+        <v>5083.35</v>
       </c>
     </row>
     <row r="222">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>195.8</v>
+        <v>192.64</v>
       </c>
     </row>
     <row r="223">
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>12632.19</v>
+        <v>12428.34</v>
       </c>
     </row>
     <row r="224">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>9776.950000000001</v>
+        <v>9619.18</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>10358.23</v>
+        <v>10191.07</v>
       </c>
     </row>
     <row r="226">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>567.08</v>
+        <v>557.9299999999999</v>
       </c>
     </row>
     <row r="227">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1826.05</v>
+        <v>1796.58</v>
       </c>
     </row>
     <row r="228">
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1368.47</v>
+        <v>1346.38</v>
       </c>
     </row>
     <row r="229">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2154.6</v>
+        <v>2119.83</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>258.05</v>
+        <v>253.89</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>35883.54</v>
+        <v>35304.47</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>37595.2</v>
+        <v>36992.41</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>5842.29</v>
+        <v>5748.62</v>
       </c>
     </row>
     <row r="234">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>22411.25</v>
+        <v>22051.92</v>
       </c>
     </row>
     <row r="235">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>45114.24</v>
+        <v>44390.89</v>
       </c>
     </row>
     <row r="236">
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1074.15</v>
+        <v>1056.93</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1611.22</v>
+        <v>1585.39</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>21482.97</v>
+        <v>21138.52</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1546.77</v>
+        <v>1521.97</v>
       </c>
     </row>
     <row r="240">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>24705.42</v>
+        <v>24309.3</v>
       </c>
     </row>
     <row r="241">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>9752.950000000001</v>
+        <v>9596.57</v>
       </c>
     </row>
     <row r="242">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2230.18</v>
+        <v>2194.42</v>
       </c>
     </row>
     <row r="243">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>17848.47</v>
+        <v>17562.29</v>
       </c>
     </row>
     <row r="244">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>7038.12</v>
+        <v>6925.27</v>
       </c>
     </row>
     <row r="245">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>26476.78</v>
+        <v>26168.7</v>
       </c>
     </row>
     <row r="246">
@@ -15461,7 +15461,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>19216.54</v>
+        <v>18992.94</v>
       </c>
     </row>
     <row r="247">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>753.1799999999999</v>
+        <v>744.42</v>
       </c>
     </row>
     <row r="248">
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>12401.45</v>
+        <v>12257.15</v>
       </c>
     </row>
     <row r="249">
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>79556.94</v>
+        <v>78631.24000000001</v>
       </c>
     </row>
     <row r="250">
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>23838.97</v>
+        <v>23561.59</v>
       </c>
     </row>
     <row r="251">
@@ -15770,7 +15770,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>31579.96</v>
+        <v>31212.51</v>
       </c>
     </row>
     <row r="252">
@@ -15831,7 +15831,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>966.73</v>
+        <v>955.48</v>
       </c>
     </row>
     <row r="253">
@@ -15892,7 +15892,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>11663.53</v>
+        <v>11527.82</v>
       </c>
     </row>
     <row r="254">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1530.66</v>
+        <v>1512.85</v>
       </c>
     </row>
     <row r="255">
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>10741.66</v>
+        <v>10616.68</v>
       </c>
     </row>
     <row r="256">
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>14763.1</v>
+        <v>14591.32</v>
       </c>
     </row>
     <row r="257">
@@ -16136,7 +16136,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3523.21</v>
+        <v>3482.21</v>
       </c>
     </row>
     <row r="258">
@@ -16197,7 +16197,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1611.22</v>
+        <v>1592.48</v>
       </c>
     </row>
     <row r="259">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4472.75</v>
+        <v>4420.71</v>
       </c>
     </row>
     <row r="260">
@@ -16319,7 +16319,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>18141.5</v>
+        <v>17930.41</v>
       </c>
     </row>
     <row r="261">
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>37853.96</v>
+        <v>37413.5</v>
       </c>
     </row>
     <row r="262">
@@ -16441,7 +16441,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3357.25</v>
+        <v>3318.19</v>
       </c>
     </row>
     <row r="263">
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>14737.32</v>
+        <v>14565.84</v>
       </c>
     </row>
     <row r="264">
@@ -16563,7 +16563,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>37388.42</v>
+        <v>36953.38</v>
       </c>
     </row>
     <row r="265">
@@ -16624,7 +16624,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>12109.98</v>
+        <v>11969.07</v>
       </c>
     </row>
     <row r="266">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>9130.26</v>
+        <v>9079.639999999999</v>
       </c>
     </row>
     <row r="267">
@@ -16746,7 +16746,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>42965.94</v>
+        <v>42727.74</v>
       </c>
     </row>
     <row r="268">
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>31649.86</v>
+        <v>31474.4</v>
       </c>
     </row>
     <row r="269">
@@ -16868,7 +16868,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>75136.17</v>
+        <v>74719.62</v>
       </c>
     </row>
     <row r="270">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>52307.83</v>
+        <v>52017.84</v>
       </c>
     </row>
     <row r="271">
@@ -16990,7 +16990,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>26953.27</v>
+        <v>26803.85</v>
       </c>
     </row>
     <row r="272">
@@ -17051,7 +17051,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>9770.84</v>
+        <v>9716.67</v>
       </c>
     </row>
     <row r="273">
@@ -17112,7 +17112,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>32224.45</v>
+        <v>32045.8</v>
       </c>
     </row>
     <row r="274">
@@ -17173,7 +17173,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>50619.53</v>
+        <v>50338.9</v>
       </c>
     </row>
     <row r="275">
@@ -17234,7 +17234,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>24022.66</v>
+        <v>23889.48</v>
       </c>
     </row>
     <row r="276">
@@ -17295,7 +17295,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>42647.55</v>
+        <v>42411.12</v>
       </c>
     </row>
     <row r="277">
@@ -17356,7 +17356,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2739.08</v>
+        <v>2723.89</v>
       </c>
     </row>
     <row r="278">
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2142.92</v>
+        <v>2131.04</v>
       </c>
     </row>
     <row r="279">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>18010.78</v>
+        <v>17910.93</v>
       </c>
     </row>
     <row r="280">
@@ -17539,7 +17539,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>38350.71</v>
+        <v>38138.1</v>
       </c>
     </row>
     <row r="281">
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>24.78</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="282">
@@ -17661,7 +17661,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>7443.4</v>
+        <v>7406.8</v>
       </c>
     </row>
     <row r="283">
@@ -17722,7 +17722,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>23631.27</v>
+        <v>23515.08</v>
       </c>
     </row>
     <row r="284">
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1374.91</v>
+        <v>1368.15</v>
       </c>
     </row>
     <row r="285">
@@ -17844,7 +17844,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>8056.11</v>
+        <v>8016.5</v>
       </c>
     </row>
     <row r="286">
@@ -17905,7 +17905,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>37580.16</v>
+        <v>37395.38</v>
       </c>
     </row>
     <row r="287">
@@ -17966,7 +17966,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>857.17</v>
+        <v>852.96</v>
       </c>
     </row>
     <row r="288">
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>117.16</v>
+        <v>116.59</v>
       </c>
     </row>
     <row r="289">
@@ -18088,7 +18088,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1628.47</v>
+        <v>1620.47</v>
       </c>
     </row>
     <row r="290">
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>7304.21</v>
+        <v>7268.3</v>
       </c>
     </row>
     <row r="291">
@@ -18210,7 +18210,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>11065.62</v>
+        <v>11011.21</v>
       </c>
     </row>
     <row r="292">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1421.1</v>
+        <v>1414.11</v>
       </c>
     </row>
     <row r="293">
@@ -18332,7 +18332,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>15789.98</v>
+        <v>15712.35</v>
       </c>
     </row>
     <row r="294">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>20408.82</v>
+        <v>20308.48</v>
       </c>
     </row>
     <row r="295">
@@ -18454,7 +18454,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>58926.64</v>
+        <v>58636.91</v>
       </c>
     </row>
     <row r="296">
@@ -18515,7 +18515,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1020.44</v>
+        <v>1015.42</v>
       </c>
     </row>
     <row r="297">
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>214.83</v>
+        <v>213.77</v>
       </c>
     </row>
     <row r="298">
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>7237.11</v>
+        <v>7201.53</v>
       </c>
     </row>
     <row r="299">
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>8893.950000000001</v>
+        <v>8850.219999999999</v>
       </c>
     </row>
     <row r="300">
@@ -18759,7 +18759,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>18947.98</v>
+        <v>18854.82</v>
       </c>
     </row>
     <row r="301">
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>73686.58</v>
+        <v>73324.28</v>
       </c>
     </row>
     <row r="302">
@@ -18881,7 +18881,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>12889.78</v>
+        <v>12826.41</v>
       </c>
     </row>
     <row r="303">
@@ -18942,7 +18942,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>64998.18</v>
+        <v>65433.24</v>
       </c>
     </row>
     <row r="304">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>32111.87</v>
+        <v>32326.81</v>
       </c>
     </row>
     <row r="305">
@@ -19064,7 +19064,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>75190.39</v>
+        <v>75693.67999999999</v>
       </c>
     </row>
     <row r="306">
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>315.8</v>
+        <v>317.91</v>
       </c>
     </row>
     <row r="307">
@@ -19186,7 +19186,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>686.46</v>
+        <v>691.0599999999999</v>
       </c>
     </row>
     <row r="308">
@@ -19247,7 +19247,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>12887.17</v>
+        <v>12973.43</v>
       </c>
     </row>
     <row r="309">
@@ -19308,7 +19308,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>7908.25</v>
+        <v>7961.19</v>
       </c>
     </row>
     <row r="310">
@@ -19369,7 +19369,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>4253.63</v>
+        <v>4282.1</v>
       </c>
     </row>
     <row r="311">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>3609.14</v>
+        <v>3633.3</v>
       </c>
     </row>
     <row r="312">
@@ -19491,7 +19491,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>429.66</v>
+        <v>432.54</v>
       </c>
     </row>
     <row r="313">
@@ -19552,7 +19552,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>13833.24</v>
+        <v>13925.83</v>
       </c>
     </row>
     <row r="314">
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>708.9400000000001</v>
+        <v>713.6799999999999</v>
       </c>
     </row>
     <row r="315">
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>28317.4</v>
+        <v>28506.94</v>
       </c>
     </row>
     <row r="316">
@@ -19735,7 +19735,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>353.09</v>
+        <v>355.46</v>
       </c>
     </row>
     <row r="317">
@@ -19796,7 +19796,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1476.05</v>
+        <v>1485.93</v>
       </c>
     </row>
     <row r="318">
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>13213.21</v>
+        <v>13301.65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18556,7 +18556,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Educación</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Educación</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Brigada de Inteligencia del Ejército</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>COB - Almacén Militar del Ejército</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valparaíso</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO CONTROL FINANCIERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Copiapo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13423,7 +13423,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Brigada de Inteligencia del Ejército</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valparaíso</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -15253,7 +15253,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15487,7 +15487,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15867,7 +15867,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Esta</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17626,7 +17626,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17763,7 +17763,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -18002,7 +18002,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
@@ -14407,7 +14407,11 @@
           <t>76.045.081-2</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17003,7 +17007,11 @@
           <t>76.045.081-2</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
